--- a/human_resources_forms/022_non_exempt_employee_dual_service_request_form--human_resources_forms.xlsx
+++ b/human_resources_forms/022_non_exempt_employee_dual_service_request_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,587 +515,292 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dual_service_request_form</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Non-Exempt Employee Dual Service Request Form</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Human-Resources Forms</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe the dual service request</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Assigned to</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Briefly describe the dual service request</t>
+          <t>Enter date in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>24h format</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Submitted by</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Additional comments</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter date in YYYY-MM-DD format</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Output File</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1110,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,12 +848,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'human_resources_forms'}</t>
+          <t>human-resources_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Human Resources Forms'}</t>
+          <t>Human-Resources Forms</t>
         </is>
       </c>
     </row>
@@ -1160,12 +865,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1177,12 +882,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1194,12 +899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1211,607 +916,182 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>output_file_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>022_non_exempt_employee_dual_service_request_form--human_resources_forms.yaml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>022 non exempt employee dual service request form--human resources forms.yaml</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>output_file_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>022_non_exempt_employee_dual_service_request_form--hrforms.yaml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>022 non exempt employee dual service request form--hrforms.yaml</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_'pending'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 'Pending'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_'approved'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': 'Approved'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'rejected'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'Rejected'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'john'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'John'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'jane'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Jane'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'today'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Today'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'yesterday'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Yesterday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'last_week'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Last Week'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'am'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'AM'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'pm'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'PM'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>output_file_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'022_non_exempt_employee_dual_service_request_form--human_resources_forms.yaml'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': '022_non_exempt_employee_dual_service_request_form--human_resources_forms.yaml'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>output_file_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'022_non_exempt_employee_dual_service_request_form--hrforms.yaml'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': '022_non_exempt_employee_dual_service_request_form--hrforms.yaml'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'chatjimmy'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'chatjimmy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'john'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'John'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'jane'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Jane'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>created_by_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_'today'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 'Today'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'yesterday'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Yesterday'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>date_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'last_week'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'Last Week'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>time_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'am'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'AM'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>time_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'pm'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'PM'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>submitted_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>submitted_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
